--- a/fhir/finnish-smart/StructureDefinition-fi-smart-practitioner-role.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-practitioner-role.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc2</t>
+    <t>2.0.0-rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-11T17:07:13+03:00</t>
+    <t>2025-06-01T15:36:45+03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/finnish-smart/StructureDefinition-fi-smart-practitioner-role.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-practitioner-role.xlsx
@@ -9,9 +9,6 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$36</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -33,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc3</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-01T15:36:45+03:00</t>
+    <t>2025-10-26T13:24:16+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1010,21 +1007,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1364,7 +1346,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1476,7 +1458,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1590,7 +1572,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -1702,7 +1684,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -1816,7 +1798,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -1930,7 +1912,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2044,7 +2026,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2158,7 +2140,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2272,7 +2254,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2388,7 +2370,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2502,7 +2484,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>154</v>
       </c>
@@ -2620,7 +2602,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>164</v>
       </c>
@@ -2734,7 +2716,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>173</v>
       </c>
@@ -2753,7 +2735,7 @@
         <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>77</v>
@@ -2846,7 +2828,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>178</v>
       </c>
@@ -2958,7 +2940,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>183</v>
       </c>
@@ -3074,7 +3056,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>194</v>
       </c>
@@ -3186,7 +3168,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>202</v>
       </c>
@@ -3298,7 +3280,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>209</v>
       </c>
@@ -3410,7 +3392,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>215</v>
       </c>
@@ -3524,7 +3506,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>221</v>
       </c>
@@ -3638,7 +3620,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>227</v>
       </c>
@@ -3750,7 +3732,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>233</v>
       </c>
@@ -3864,7 +3846,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>236</v>
       </c>
@@ -3980,7 +3962,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>241</v>
       </c>
@@ -4092,7 +4074,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>247</v>
       </c>
@@ -4204,7 +4186,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>250</v>
       </c>
@@ -4318,7 +4300,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>255</v>
       </c>
@@ -4432,7 +4414,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>258</v>
       </c>
@@ -4544,7 +4526,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>261</v>
       </c>
@@ -4656,7 +4638,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>262</v>
       </c>
@@ -4770,7 +4752,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>263</v>
       </c>
@@ -4886,7 +4868,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>264</v>
       </c>
@@ -4998,7 +4980,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>267</v>
       </c>
@@ -5110,7 +5092,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>270</v>
       </c>
@@ -5222,7 +5204,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>273</v>
       </c>
@@ -5337,24 +5319,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN36">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI35">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>